--- a/jpcore-r4/feature/swg2-dental/StructureDefinition-jp-observation-dentaloral-toothtreatmentcondition.xlsx
+++ b/jpcore-r4/feature/swg2-dental/StructureDefinition-jp-observation-dentaloral-toothtreatmentcondition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3793" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4747" uniqueCount="601">
   <si>
     <t>Property</t>
   </si>
@@ -747,6 +747,9 @@
     <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS</t>
+  </si>
+  <si>
     <t>Coding.system</t>
   </si>
   <si>
@@ -795,6 +798,9 @@
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
   </si>
   <si>
+    <t>procedure</t>
+  </si>
+  <si>
     <t>Coding.code</t>
   </si>
   <si>
@@ -817,6 +823,9 @@
   </si>
   <si>
     <t>システムを知らない読者のために、コードの人間の読み取り可能な意味を持ち込むことができる必要があります。 / Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Procedure</t>
   </si>
   <si>
     <t>Coding.display</t>
@@ -946,6 +955,9 @@
     <t>このObservationに関する詳細分類、JP_ObservationDentalCategory_VSより選択する、必須項目</t>
   </si>
   <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationDentalCategory_VS</t>
+  </si>
+  <si>
     <t>Observation.category:third.id</t>
   </si>
   <si>
@@ -964,16 +976,22 @@
     <t>Observation.category:third.coding.system</t>
   </si>
   <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationDentalCategory_CS</t>
+  </si>
+  <si>
     <t>Observation.category:third.coding.version</t>
   </si>
   <si>
     <t>Observation.category:third.coding.code</t>
   </si>
   <si>
+    <t>DO-1-02</t>
+  </si>
+  <si>
     <t>Observation.category:third.coding.display</t>
   </si>
   <si>
-    <t>Tooth Treatment Condition</t>
+    <t>ToothTreatmentCondition</t>
   </si>
   <si>
     <t>Observation.category:third.coding.userSelected</t>
@@ -1340,10 +1358,7 @@
 2.厚生労働省標準標準歯式マスタ、レセプト電算処理用コード</t>
   </si>
   <si>
-    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalBodySite_VS</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1356,6 +1371,34 @@
   </si>
   <si>
     <t>718497002 |Inherent location|</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.id</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.extension</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.extension:bodyStructure</t>
+  </si>
+  <si>
+    <t>bodyStructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_DentalOral_BodyStructure}
+</t>
+  </si>
+  <si>
+    <t>特定の歯の歯面</t>
+  </si>
+  <si>
+    <t>特定の歯の歯面を格納するための拡張</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.coding</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.text</t>
   </si>
   <si>
     <t>Observation.method</t>
@@ -1671,6 +1714,118 @@
   <si>
     <t>&lt; 363787002 |Observable entity| OR  &lt; 386053000 |Evaluation procedure|</t>
+  </si>
+  <si>
+    <t>Observation.component.code.id</t>
+  </si>
+  <si>
+    <t>Observation.component.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:primary</t>
+  </si>
+  <si>
+    <t>primary</t>
+  </si>
+  <si>
+    <t>細かい粒度の現存歯の処置状態</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalPresentTeethObservation_VS</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:primary.id</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:primary.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:primary.system</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.system</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_DentalPresentTeethObservation_CS</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:primary.version</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:primary.code</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.code</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:primary.display</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:primary.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:sub</t>
+  </si>
+  <si>
+    <t>sub</t>
+  </si>
+  <si>
+    <t>粗い粒度の現存歯の処置状態</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalSimplePresentTeethObservation_VS</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:sub.id</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:sub.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:sub.system</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_DentalSimplePresentTeethObservation_CS</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:sub.version</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:sub.code</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:sub.display</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:sub.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.component.code.text</t>
   </si>
   <si>
     <t>Observation.component.value[x]</t>
@@ -2037,12 +2192,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP98"/>
+  <dimension ref="A1:AP123"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="47.2890625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="55.19921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="47.40625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="14.1484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2065,7 +2220,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="105.8828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.09375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="72.98046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -4624,7 +4779,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>94</v>
@@ -4658,7 +4813,7 @@
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>83</v>
+        <v>234</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4700,7 +4855,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4721,10 +4876,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4735,10 +4890,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4764,13 +4919,13 @@
         <v>203</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4820,7 +4975,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4841,10 +4996,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4855,10 +5010,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4884,21 +5039,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>83</v>
+        <v>251</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -4940,7 +5095,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4961,10 +5116,10 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -4975,10 +5130,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5004,14 +5159,14 @@
         <v>203</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5021,7 +5176,7 @@
         <v>83</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>83</v>
+        <v>260</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>83</v>
@@ -5060,7 +5215,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5081,10 +5236,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5095,10 +5250,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5121,19 +5276,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5182,7 +5337,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5203,10 +5358,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5217,10 +5372,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5246,16 +5401,16 @@
         <v>203</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5304,7 +5459,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5325,10 +5480,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5339,13 +5494,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>186</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>83</v>
@@ -5370,10 +5525,10 @@
         <v>188</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>200</v>
@@ -5461,7 +5616,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>202</v>
@@ -5579,7 +5734,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>209</v>
@@ -5699,7 +5854,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>215</v>
@@ -5821,7 +5976,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>225</v>
@@ -5939,7 +6094,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>227</v>
@@ -6059,7 +6214,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>229</v>
@@ -6104,7 +6259,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6146,7 +6301,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6167,10 +6322,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6181,10 +6336,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6210,13 +6365,13 @@
         <v>203</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6266,7 +6421,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6287,10 +6442,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6301,10 +6456,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6330,21 +6485,21 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6386,7 +6541,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6407,10 +6562,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6421,10 +6576,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6450,14 +6605,14 @@
         <v>203</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6467,7 +6622,7 @@
         <v>83</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>83</v>
@@ -6506,7 +6661,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6527,10 +6682,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6541,10 +6696,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6567,19 +6722,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6628,7 +6783,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6649,10 +6804,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6663,10 +6818,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6692,16 +6847,16 @@
         <v>203</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6750,7 +6905,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6771,10 +6926,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6785,13 +6940,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>186</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>83</v>
@@ -6816,10 +6971,10 @@
         <v>188</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>200</v>
@@ -6850,11 +7005,11 @@
         <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>118</v>
+        <v>178</v>
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>192</v>
+        <v>303</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6907,7 +7062,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>202</v>
@@ -7025,7 +7180,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>209</v>
@@ -7145,7 +7300,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>215</v>
@@ -7267,7 +7422,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>225</v>
@@ -7385,7 +7540,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>227</v>
@@ -7505,7 +7660,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>229</v>
@@ -7516,7 +7671,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>94</v>
@@ -7550,7 +7705,7 @@
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>83</v>
+        <v>310</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>83</v>
@@ -7592,7 +7747,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7613,10 +7768,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7627,10 +7782,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7656,13 +7811,13 @@
         <v>203</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7712,7 +7867,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7733,10 +7888,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7747,10 +7902,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7776,21 +7931,21 @@
         <v>114</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>83</v>
+        <v>313</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>83</v>
@@ -7832,7 +7987,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7853,10 +8008,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7867,10 +8022,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7896,14 +8051,14 @@
         <v>203</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7913,7 +8068,7 @@
         <v>83</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>83</v>
@@ -7952,7 +8107,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7973,10 +8128,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -7987,10 +8142,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8013,19 +8168,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8074,7 +8229,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8095,10 +8250,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8109,10 +8264,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8138,16 +8293,16 @@
         <v>203</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8196,7 +8351,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8217,10 +8372,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8231,14 +8386,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8260,16 +8415,16 @@
         <v>188</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8294,31 +8449,31 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>94</v>
@@ -8333,30 +8488,30 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8471,10 +8626,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8591,10 +8746,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8620,10 +8775,10 @@
         <v>216</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>219</v>
@@ -8713,10 +8868,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8831,10 +8986,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8951,10 +9106,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8996,7 +9151,7 @@
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>83</v>
@@ -9038,7 +9193,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9059,10 +9214,10 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -9073,10 +9228,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9102,13 +9257,13 @@
         <v>203</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9158,7 +9313,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9179,10 +9334,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9193,10 +9348,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9222,21 +9377,21 @@
         <v>114</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>83</v>
@@ -9278,7 +9433,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9299,10 +9454,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9313,10 +9468,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9342,14 +9497,14 @@
         <v>203</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9359,7 +9514,7 @@
         <v>83</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>83</v>
@@ -9398,7 +9553,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9419,10 +9574,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9433,10 +9588,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9459,19 +9614,19 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9520,7 +9675,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9541,10 +9696,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9555,10 +9710,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9584,16 +9739,16 @@
         <v>203</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9642,7 +9797,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9663,10 +9818,10 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9677,10 +9832,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9703,19 +9858,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9764,7 +9919,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9779,19 +9934,19 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -9799,10 +9954,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9825,7 +9980,7 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>162</v>
@@ -9834,7 +9989,7 @@
         <v>162</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9884,7 +10039,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9905,13 +10060,13 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -9919,14 +10074,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9945,19 +10100,19 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10006,7 +10161,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10021,19 +10176,19 @@
         <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10041,14 +10196,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10067,19 +10222,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10128,7 +10283,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10143,19 +10298,19 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10163,10 +10318,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10189,16 +10344,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10248,7 +10403,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10269,13 +10424,13 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10283,10 +10438,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10309,19 +10464,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10370,7 +10525,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10385,19 +10540,19 @@
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -10405,10 +10560,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10434,16 +10589,16 @@
         <v>188</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10492,7 +10647,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10501,7 +10656,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -10510,27 +10665,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10556,16 +10711,16 @@
         <v>188</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10590,32 +10745,32 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="Z71" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AA71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>398</v>
-      </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
       </c>
@@ -10623,7 +10778,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -10638,7 +10793,7 @@
         <v>137</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -10649,14 +10804,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10684,10 +10839,10 @@
         <v>162</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10712,13 +10867,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10736,7 +10891,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10754,27 +10909,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10797,7 +10952,7 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="L73" t="s" s="2">
         <v>162</v>
@@ -10806,10 +10961,10 @@
         <v>162</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -10858,7 +11013,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10879,10 +11034,10 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -10893,10 +11048,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10922,13 +11077,13 @@
         <v>188</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10954,13 +11109,11 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>426</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -10978,7 +11131,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10996,27 +11149,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11039,20 +11192,16 @@
         <v>83</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>433</v>
+        <v>204</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>435</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>83</v>
       </c>
@@ -11076,13 +11225,13 @@
         <v>83</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>317</v>
+        <v>83</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>436</v>
+        <v>83</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>437</v>
+        <v>83</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -11100,7 +11249,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>432</v>
+        <v>206</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11112,7 +11261,7 @@
         <v>83</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>83</v>
@@ -11121,10 +11270,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>438</v>
+        <v>83</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>439</v>
+        <v>207</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11135,21 +11284,21 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>83</v>
@@ -11161,16 +11310,16 @@
         <v>83</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>441</v>
+        <v>140</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>162</v>
+        <v>210</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>442</v>
+        <v>143</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11208,59 +11357,61 @@
         <v>83</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>83</v>
+        <v>211</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>83</v>
+        <v>212</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>83</v>
+        <v>194</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>440</v>
+        <v>213</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>443</v>
+        <v>83</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>444</v>
+        <v>83</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>445</v>
+        <v>207</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>446</v>
+        <v>83</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C77" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>440</v>
+      </c>
       <c r="D77" t="s" s="2">
         <v>83</v>
       </c>
@@ -11269,7 +11420,7 @@
         <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>83</v>
@@ -11281,17 +11432,15 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>83</v>
@@ -11340,45 +11489,45 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>447</v>
+        <v>213</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>451</v>
+        <v>83</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>452</v>
+        <v>83</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>453</v>
+        <v>83</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>454</v>
+        <v>83</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11398,22 +11547,22 @@
         <v>83</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>456</v>
+        <v>216</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>162</v>
+        <v>218</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>457</v>
+        <v>219</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>458</v>
+        <v>220</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -11462,7 +11611,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>455</v>
+        <v>221</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11474,7 +11623,7 @@
         <v>83</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>459</v>
+        <v>106</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>83</v>
@@ -11483,10 +11632,10 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>460</v>
+        <v>222</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>461</v>
+        <v>223</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11497,10 +11646,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>462</v>
+        <v>445</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>462</v>
+        <v>445</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11520,19 +11669,23 @@
         <v>83</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K79" t="s" s="2">
         <v>203</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>204</v>
+        <v>276</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
       </c>
@@ -11580,7 +11733,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>206</v>
+        <v>280</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11592,7 +11745,7 @@
         <v>83</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>83</v>
@@ -11601,10 +11754,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>83</v>
+        <v>281</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>207</v>
+        <v>282</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11615,21 +11768,21 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>463</v>
+        <v>446</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>463</v>
+        <v>446</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>83</v>
@@ -11641,18 +11794,20 @@
         <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>141</v>
+        <v>447</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>210</v>
+        <v>447</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O80" s="2"/>
+        <v>448</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
       </c>
@@ -11676,13 +11831,13 @@
         <v>83</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>83</v>
+        <v>323</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>83</v>
+        <v>450</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>83</v>
+        <v>451</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>83</v>
@@ -11700,19 +11855,19 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>213</v>
+        <v>446</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>83</v>
@@ -11721,10 +11876,10 @@
         <v>83</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>83</v>
+        <v>452</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>207</v>
+        <v>453</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -11735,46 +11890,44 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>465</v>
+        <v>83</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>140</v>
+        <v>455</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>466</v>
+        <v>162</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>467</v>
+        <v>162</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>83</v>
       </c>
@@ -11822,45 +11975,45 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>468</v>
+        <v>454</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>83</v>
+        <v>457</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>83</v>
+        <v>458</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>137</v>
+        <v>459</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>83</v>
+        <v>460</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11883,15 +12036,17 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>463</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -11940,7 +12095,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -11949,7 +12104,7 @@
         <v>94</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>473</v>
+        <v>83</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>106</v>
@@ -11958,27 +12113,27 @@
         <v>83</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>83</v>
+        <v>465</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>83</v>
+        <v>468</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11989,7 +12144,7 @@
         <v>81</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>83</v>
@@ -12004,13 +12159,17 @@
         <v>470</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>477</v>
+        <v>162</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>472</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
       </c>
@@ -12058,19 +12217,19 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>106</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>83</v>
@@ -12082,7 +12241,7 @@
         <v>474</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12093,10 +12252,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12119,20 +12278,16 @@
         <v>83</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>481</v>
+        <v>204</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>484</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>83</v>
       </c>
@@ -12156,13 +12311,13 @@
         <v>83</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>485</v>
+        <v>83</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>486</v>
+        <v>83</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>83</v>
@@ -12180,7 +12335,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>480</v>
+        <v>206</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12192,19 +12347,19 @@
         <v>83</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>487</v>
+        <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>488</v>
+        <v>83</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>415</v>
+        <v>207</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12215,14 +12370,14 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12241,20 +12396,18 @@
         <v>83</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>188</v>
+        <v>140</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>490</v>
+        <v>141</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>491</v>
+        <v>210</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>493</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>83</v>
       </c>
@@ -12278,13 +12431,13 @@
         <v>83</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>317</v>
+        <v>83</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>494</v>
+        <v>83</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>495</v>
+        <v>83</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>83</v>
@@ -12302,7 +12455,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>489</v>
+        <v>213</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12314,19 +12467,19 @@
         <v>83</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>487</v>
+        <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>488</v>
+        <v>83</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>415</v>
+        <v>207</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12337,43 +12490,45 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>496</v>
+        <v>478</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>496</v>
+        <v>478</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>83</v>
+        <v>479</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>497</v>
+        <v>140</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>498</v>
+        <v>480</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>481</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O86" t="s" s="2">
-        <v>500</v>
+        <v>149</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12422,19 +12577,19 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>496</v>
+        <v>482</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>83</v>
@@ -12446,7 +12601,7 @@
         <v>83</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>501</v>
+        <v>137</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12457,10 +12612,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>502</v>
+        <v>483</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>502</v>
+        <v>483</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12483,13 +12638,13 @@
         <v>83</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>203</v>
+        <v>484</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>503</v>
+        <v>485</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>504</v>
+        <v>486</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12540,7 +12695,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>502</v>
+        <v>483</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12549,7 +12704,7 @@
         <v>94</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>83</v>
+        <v>487</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>106</v>
@@ -12561,10 +12716,10 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>505</v>
+        <v>489</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12575,10 +12730,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>506</v>
+        <v>490</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>506</v>
+        <v>490</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12589,7 +12744,7 @@
         <v>81</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>83</v>
@@ -12598,20 +12753,18 @@
         <v>83</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>507</v>
+        <v>484</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>508</v>
+        <v>491</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>509</v>
-      </c>
+        <v>492</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>83</v>
@@ -12660,16 +12813,16 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>506</v>
+        <v>490</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>83</v>
+        <v>487</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>106</v>
@@ -12681,10 +12834,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>510</v>
+        <v>488</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>511</v>
+        <v>493</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12695,10 +12848,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>512</v>
+        <v>494</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>512</v>
+        <v>494</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12709,7 +12862,7 @@
         <v>81</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>83</v>
@@ -12718,21 +12871,23 @@
         <v>83</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>513</v>
+        <v>188</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>162</v>
+        <v>495</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>162</v>
+        <v>496</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="O89" s="2"/>
+        <v>497</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>498</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>83</v>
       </c>
@@ -12756,13 +12911,13 @@
         <v>83</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>83</v>
+        <v>499</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>83</v>
+        <v>500</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>83</v>
@@ -12780,13 +12935,13 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>512</v>
+        <v>494</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>83</v>
@@ -12798,13 +12953,13 @@
         <v>83</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>83</v>
+        <v>501</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>515</v>
+        <v>421</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -12815,10 +12970,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12838,22 +12993,22 @@
         <v>83</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>456</v>
+        <v>188</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -12878,13 +13033,13 @@
         <v>83</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>83</v>
+        <v>323</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>83</v>
+        <v>508</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>83</v>
+        <v>509</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -12902,7 +13057,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -12920,13 +13075,13 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>83</v>
+        <v>501</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>521</v>
+        <v>421</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -12937,10 +13092,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12963,16 +13118,18 @@
         <v>83</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>203</v>
+        <v>511</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>204</v>
+        <v>512</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>205</v>
+        <v>513</v>
       </c>
       <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+      <c r="O91" t="s" s="2">
+        <v>514</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
       </c>
@@ -13020,7 +13177,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>206</v>
+        <v>510</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13032,7 +13189,7 @@
         <v>83</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>83</v>
@@ -13044,7 +13201,7 @@
         <v>83</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>207</v>
+        <v>515</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
@@ -13055,21 +13212,21 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>83</v>
@@ -13081,17 +13238,15 @@
         <v>83</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>140</v>
+        <v>203</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>141</v>
+        <v>517</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>518</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13140,19 +13295,19 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>213</v>
+        <v>516</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>83</v>
@@ -13161,10 +13316,10 @@
         <v>83</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>83</v>
+        <v>488</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>207</v>
+        <v>519</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13175,14 +13330,14 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>465</v>
+        <v>83</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13195,26 +13350,24 @@
         <v>83</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J93" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>140</v>
+        <v>521</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>466</v>
+        <v>522</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>467</v>
+        <v>522</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>523</v>
+      </c>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>83</v>
       </c>
@@ -13262,7 +13415,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>468</v>
+        <v>520</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13274,7 +13427,7 @@
         <v>83</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>83</v>
@@ -13283,10 +13436,10 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>83</v>
+        <v>524</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>137</v>
+        <v>525</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
@@ -13297,10 +13450,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13308,10 +13461,10 @@
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>83</v>
@@ -13323,20 +13476,18 @@
         <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>188</v>
+        <v>527</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>526</v>
+        <v>162</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>527</v>
+        <v>162</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="O94" t="s" s="2">
-        <v>316</v>
-      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>83</v>
       </c>
@@ -13360,13 +13511,13 @@
         <v>83</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>317</v>
+        <v>83</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>318</v>
+        <v>83</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>319</v>
+        <v>83</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>83</v>
@@ -13384,13 +13535,13 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>83</v>
@@ -13402,16 +13553,16 @@
         <v>83</v>
       </c>
       <c r="AL94" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="AM94" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>323</v>
-      </c>
       <c r="AO94" t="s" s="2">
-        <v>324</v>
+        <v>83</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>83</v>
@@ -13433,7 +13584,7 @@
         <v>81</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>83</v>
@@ -13445,19 +13596,19 @@
         <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="N95" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="O95" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13512,7 +13663,7 @@
         <v>81</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>83</v>
@@ -13524,19 +13675,19 @@
         <v>83</v>
       </c>
       <c r="AL95" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="AM95" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>396</v>
-      </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>397</v>
+        <v>83</v>
       </c>
     </row>
     <row r="96">
@@ -13567,20 +13718,16 @@
         <v>83</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>537</v>
+        <v>204</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>83</v>
       </c>
@@ -13604,13 +13751,13 @@
         <v>83</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>402</v>
+        <v>83</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>403</v>
+        <v>83</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>404</v>
+        <v>83</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>83</v>
@@ -13628,7 +13775,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>536</v>
+        <v>206</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13637,10 +13784,10 @@
         <v>94</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>405</v>
+        <v>83</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>83</v>
@@ -13649,10 +13796,10 @@
         <v>83</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>406</v>
+        <v>207</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
@@ -13663,14 +13810,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>408</v>
+        <v>139</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13689,20 +13836,18 @@
         <v>83</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>188</v>
+        <v>140</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>541</v>
+        <v>141</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>542</v>
+        <v>210</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>544</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>83</v>
       </c>
@@ -13726,13 +13871,13 @@
         <v>83</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>402</v>
+        <v>83</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>411</v>
+        <v>83</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>412</v>
+        <v>83</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>83</v>
@@ -13750,7 +13895,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>540</v>
+        <v>213</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13762,37 +13907,37 @@
         <v>83</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>413</v>
+        <v>83</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>414</v>
+        <v>83</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>415</v>
+        <v>207</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>416</v>
+        <v>83</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>83</v>
+        <v>479</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -13805,25 +13950,25 @@
         <v>83</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>546</v>
+        <v>480</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>547</v>
+        <v>481</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>548</v>
+        <v>143</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>549</v>
+        <v>149</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -13872,7 +14017,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>545</v>
+        <v>482</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -13884,24 +14029,3042 @@
         <v>83</v>
       </c>
       <c r="AJ98" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP98" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="P99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AK98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP98" t="s" s="2">
+      <c r="AK99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
+      <c r="P100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP100" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="P102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AC102" s="2"/>
+      <c r="AD102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="C103" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="D103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="P103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="Y103" s="2"/>
+      <c r="Z103" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP104" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP105" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP106" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP107" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="P108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP108" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="P109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP109" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="P110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP110" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="C111" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="D111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="P111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="Y111" s="2"/>
+      <c r="Z111" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP111" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
+      <c r="P112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP112" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O113" s="2"/>
+      <c r="P113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP113" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="O114" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="P114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP114" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="O115" s="2"/>
+      <c r="P115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP115" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="P116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AO116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP116" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="N117" s="2"/>
+      <c r="O117" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="P117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AO117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP117" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="P118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AO118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP118" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="P119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AO119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP119" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="P120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AO120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP120" t="s" s="2">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="P121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AO121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP121" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="O122" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="P122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AO122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP122" t="s" s="2">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="O123" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="P123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AO123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP123" t="s" s="2">
         <v>83</v>
       </c>
     </row>
